--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298089</v>
+        <v>129298202</v>
       </c>
       <c r="B4" t="n">
         <v>80144</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555796</v>
+        <v>555795</v>
       </c>
       <c r="R4" t="n">
-        <v>7045752</v>
+        <v>7045772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298202</v>
+        <v>129298089</v>
       </c>
       <c r="B5" t="n">
         <v>80144</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555795</v>
+        <v>555796</v>
       </c>
       <c r="R5" t="n">
-        <v>7045772</v>
+        <v>7045752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297825</v>
+        <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555773</v>
+        <v>555786</v>
       </c>
       <c r="R6" t="n">
-        <v>7045733</v>
+        <v>7045728</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297875</v>
+        <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555786</v>
+        <v>555773</v>
       </c>
       <c r="R7" t="n">
-        <v>7045728</v>
+        <v>7045733</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B12" t="n">
-        <v>97540</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R12" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R13" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,44 +1955,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298104</v>
+        <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>97547</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555794</v>
+        <v>555767</v>
       </c>
       <c r="R14" t="n">
-        <v>7045772</v>
+        <v>7045714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297901</v>
       </c>
       <c r="B2" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129298103</v>
       </c>
       <c r="B3" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298202</v>
+        <v>129298089</v>
       </c>
       <c r="B4" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555795</v>
+        <v>555796</v>
       </c>
       <c r="R4" t="n">
-        <v>7045772</v>
+        <v>7045752</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298089</v>
+        <v>129298202</v>
       </c>
       <c r="B5" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555796</v>
+        <v>555795</v>
       </c>
       <c r="R5" t="n">
-        <v>7045752</v>
+        <v>7045772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129297871</v>
       </c>
       <c r="B8" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129298019</v>
       </c>
       <c r="B9" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129297796</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>129298012</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>80146</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R12" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298104</v>
+        <v>129298369</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555794</v>
+        <v>555752</v>
       </c>
       <c r="R13" t="n">
-        <v>7045772</v>
+        <v>7045712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,12 +1955,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
         <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298104</v>
+        <v>129297836</v>
       </c>
       <c r="B12" t="n">
-        <v>80146</v>
+        <v>97549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555794</v>
+        <v>555767</v>
       </c>
       <c r="R12" t="n">
-        <v>7045772</v>
+        <v>7045714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R13" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,44 +1955,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B14" t="n">
-        <v>97549</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R14" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>129297836</v>
       </c>
       <c r="B12" t="n">
-        <v>97549</v>
+        <v>97575</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298104</v>
+        <v>129298369</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555794</v>
+        <v>555752</v>
       </c>
       <c r="R13" t="n">
-        <v>7045772</v>
+        <v>7045712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,22 +1955,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R14" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298089</v>
+        <v>129298202</v>
       </c>
       <c r="B4" t="n">
         <v>80146</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555796</v>
+        <v>555795</v>
       </c>
       <c r="R4" t="n">
-        <v>7045752</v>
+        <v>7045772</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298202</v>
+        <v>129298089</v>
       </c>
       <c r="B5" t="n">
         <v>80146</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555795</v>
+        <v>555796</v>
       </c>
       <c r="R5" t="n">
-        <v>7045772</v>
+        <v>7045752</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B12" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R12" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R13" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,44 +1955,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298104</v>
+        <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>97576</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555794</v>
+        <v>555767</v>
       </c>
       <c r="R14" t="n">
-        <v>7045772</v>
+        <v>7045714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129298202</v>
+        <v>129298089</v>
       </c>
       <c r="B4" t="n">
         <v>80146</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555795</v>
+        <v>555796</v>
       </c>
       <c r="R4" t="n">
-        <v>7045772</v>
+        <v>7045752</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129298089</v>
+        <v>129298202</v>
       </c>
       <c r="B5" t="n">
         <v>80146</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555796</v>
+        <v>555795</v>
       </c>
       <c r="R5" t="n">
-        <v>7045752</v>
+        <v>7045772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298369</v>
+        <v>129297836</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>97577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555752</v>
+        <v>555767</v>
       </c>
       <c r="R12" t="n">
-        <v>7045712</v>
+        <v>7045714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1967,32 +1967,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B14" t="n">
-        <v>97576</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R14" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297901</v>
       </c>
       <c r="B2" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129298103</v>
       </c>
       <c r="B3" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129298089</v>
       </c>
       <c r="B4" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129298202</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129297871</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129298019</v>
       </c>
       <c r="B9" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129297796</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>129298012</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>129297836</v>
       </c>
       <c r="B12" t="n">
-        <v>97577</v>
+        <v>97581</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298104</v>
+        <v>129298369</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555794</v>
+        <v>555752</v>
       </c>
       <c r="R13" t="n">
-        <v>7045772</v>
+        <v>7045712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,22 +1955,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R14" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297901</v>
       </c>
       <c r="B2" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129298103</v>
       </c>
       <c r="B3" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129298089</v>
       </c>
       <c r="B4" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129298202</v>
       </c>
       <c r="B5" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129297871</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129298019</v>
       </c>
       <c r="B9" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129297796</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>129298012</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B12" t="n">
-        <v>97581</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R12" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R13" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,44 +1955,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298104</v>
+        <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>97583</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555794</v>
+        <v>555767</v>
       </c>
       <c r="R14" t="n">
-        <v>7045772</v>
+        <v>7045714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298369</v>
+        <v>129297836</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555752</v>
+        <v>555767</v>
       </c>
       <c r="R12" t="n">
-        <v>7045712</v>
+        <v>7045714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1967,32 +1967,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B14" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R14" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297875</v>
+        <v>129297825</v>
       </c>
       <c r="B6" t="n">
         <v>98724</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555786</v>
+        <v>555773</v>
       </c>
       <c r="R6" t="n">
-        <v>7045728</v>
+        <v>7045733</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297825</v>
+        <v>129297875</v>
       </c>
       <c r="B7" t="n">
         <v>98724</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555773</v>
+        <v>555786</v>
       </c>
       <c r="R7" t="n">
-        <v>7045733</v>
+        <v>7045728</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B12" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R12" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1967,32 +1967,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298369</v>
+        <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555752</v>
+        <v>555767</v>
       </c>
       <c r="R14" t="n">
-        <v>7045712</v>
+        <v>7045714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297825</v>
+        <v>129297875</v>
       </c>
       <c r="B6" t="n">
         <v>98724</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555773</v>
+        <v>555786</v>
       </c>
       <c r="R6" t="n">
-        <v>7045733</v>
+        <v>7045728</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297875</v>
+        <v>129297825</v>
       </c>
       <c r="B7" t="n">
         <v>98724</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555786</v>
+        <v>555773</v>
       </c>
       <c r="R7" t="n">
-        <v>7045728</v>
+        <v>7045733</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1860,32 +1860,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298104</v>
+        <v>129297836</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>97598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555794</v>
+        <v>555767</v>
       </c>
       <c r="R13" t="n">
-        <v>7045772</v>
+        <v>7045714</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,32 +1967,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297836</v>
+        <v>129298104</v>
       </c>
       <c r="B14" t="n">
-        <v>97595</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555767</v>
+        <v>555794</v>
       </c>
       <c r="R14" t="n">
-        <v>7045714</v>
+        <v>7045772</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298369</v>
+        <v>129297836</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555752</v>
+        <v>555767</v>
       </c>
       <c r="R12" t="n">
-        <v>7045712</v>
+        <v>7045714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,44 +1848,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B13" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R13" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,12 +1955,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2072,6 +2072,122 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129603223</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80149</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grössjöberget, Grössjöberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555773</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7045771</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-08</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Klara Högberg Nordqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Klara Högberg Nordqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297836</v>
+        <v>129298104</v>
       </c>
       <c r="B12" t="n">
-        <v>97598</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555767</v>
+        <v>555794</v>
       </c>
       <c r="R12" t="n">
-        <v>7045714</v>
+        <v>7045772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,32 +1967,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298104</v>
+        <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555794</v>
+        <v>555767</v>
       </c>
       <c r="R14" t="n">
-        <v>7045772</v>
+        <v>7045714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297875</v>
+        <v>129297825</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555786</v>
+        <v>555773</v>
       </c>
       <c r="R6" t="n">
-        <v>7045728</v>
+        <v>7045733</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297825</v>
+        <v>129297875</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555773</v>
+        <v>555786</v>
       </c>
       <c r="R7" t="n">
-        <v>7045733</v>
+        <v>7045728</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298104</v>
+        <v>129298369</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555794</v>
+        <v>555752</v>
       </c>
       <c r="R12" t="n">
-        <v>7045772</v>
+        <v>7045712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>80149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R13" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,12 +1955,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129297825</v>
+        <v>129297875</v>
       </c>
       <c r="B6" t="n">
         <v>98727</v>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1142,13 +1142,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555773</v>
+        <v>555786</v>
       </c>
       <c r="R6" t="n">
-        <v>7045733</v>
+        <v>7045728</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,7 +1214,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129297875</v>
+        <v>129297825</v>
       </c>
       <c r="B7" t="n">
         <v>98727</v>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>555786</v>
+        <v>555773</v>
       </c>
       <c r="R7" t="n">
-        <v>7045728</v>
+        <v>7045733</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298369</v>
+        <v>129297836</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555752</v>
+        <v>555767</v>
       </c>
       <c r="R12" t="n">
-        <v>7045712</v>
+        <v>7045714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,12 +1848,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1967,32 +1967,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129297836</v>
+        <v>129298369</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555767</v>
+        <v>555752</v>
       </c>
       <c r="R14" t="n">
-        <v>7045714</v>
+        <v>7045712</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -1753,32 +1753,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129297836</v>
+        <v>129298104</v>
       </c>
       <c r="B12" t="n">
-        <v>97598</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555767</v>
+        <v>555794</v>
       </c>
       <c r="R12" t="n">
-        <v>7045714</v>
+        <v>7045772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298104</v>
+        <v>129298369</v>
       </c>
       <c r="B13" t="n">
-        <v>80149</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555794</v>
+        <v>555752</v>
       </c>
       <c r="R13" t="n">
-        <v>7045772</v>
+        <v>7045712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,44 +1955,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129298369</v>
+        <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2002,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555752</v>
+        <v>555767</v>
       </c>
       <c r="R14" t="n">
-        <v>7045712</v>
+        <v>7045714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2062,12 +2062,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297901</v>
       </c>
       <c r="B2" t="n">
-        <v>80178</v>
+        <v>80204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129298103</v>
       </c>
       <c r="B3" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129298089</v>
       </c>
       <c r="B4" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129298202</v>
       </c>
       <c r="B5" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129297871</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129298019</v>
       </c>
       <c r="B9" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129297796</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>129298012</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
         <v>129298104</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>129298369</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>129603223</v>
       </c>
       <c r="B15" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297901</v>
       </c>
       <c r="B2" t="n">
-        <v>80204</v>
+        <v>80209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129298103</v>
       </c>
       <c r="B3" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129298089</v>
       </c>
       <c r="B4" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129298202</v>
       </c>
       <c r="B5" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129297871</v>
       </c>
       <c r="B8" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129298019</v>
       </c>
       <c r="B9" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129297796</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>129298012</v>
       </c>
       <c r="B11" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298104</v>
+        <v>129298369</v>
       </c>
       <c r="B12" t="n">
-        <v>80175</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555794</v>
+        <v>555752</v>
       </c>
       <c r="R12" t="n">
-        <v>7045772</v>
+        <v>7045712</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B13" t="n">
-        <v>79070</v>
+        <v>80180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R13" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,12 +1955,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
         <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>129603223</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>80180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129297901</v>
       </c>
       <c r="B2" t="n">
-        <v>80209</v>
+        <v>80210</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129298103</v>
       </c>
       <c r="B3" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>129298089</v>
       </c>
       <c r="B4" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>129298202</v>
       </c>
       <c r="B5" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129297875</v>
       </c>
       <c r="B6" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>129297825</v>
       </c>
       <c r="B7" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>129297871</v>
       </c>
       <c r="B8" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129298019</v>
       </c>
       <c r="B9" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         <v>129297796</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>129298012</v>
       </c>
       <c r="B11" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129298369</v>
+        <v>129298104</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>80181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1764,21 +1764,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555752</v>
+        <v>555794</v>
       </c>
       <c r="R12" t="n">
-        <v>7045712</v>
+        <v>7045772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1848,22 +1848,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Filippa Paperin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129298104</v>
+        <v>129298369</v>
       </c>
       <c r="B13" t="n">
-        <v>80180</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>555794</v>
+        <v>555752</v>
       </c>
       <c r="R13" t="n">
-        <v>7045772</v>
+        <v>7045712</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1955,12 +1955,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Filippa Paperin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1970,7 +1970,7 @@
         <v>129297836</v>
       </c>
       <c r="B14" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>129603223</v>
       </c>
       <c r="B15" t="n">
-        <v>80180</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -2077,7 +2077,7 @@
         <v>129603223</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>80186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -2077,7 +2077,7 @@
         <v>129603223</v>
       </c>
       <c r="B15" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40967-2025 artfynd.xlsx
+++ b/artfynd/A 40967-2025 artfynd.xlsx
@@ -2077,7 +2077,7 @@
         <v>129603223</v>
       </c>
       <c r="B15" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
